--- a/3DAG and 2D Tree/Data Summaries/Gowalla 120143 points 1 - 10,000.xlsx
+++ b/3DAG and 2D Tree/Data Summaries/Gowalla 120143 points 1 - 10,000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cvinc\Desktop\College\Internship\Github\Multi-Dimensional-Data-Structure\3DAG and 2D Tree\Data Summaries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B40B1AA2-8A4D-4E23-8467-ACDE702639C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E816849-62B4-4D20-A32D-1D5A99B9DE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{428F074D-1793-4279-8FD6-82BE55EE023D}"/>
   </bookViews>
@@ -2298,31 +2298,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Comp</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2436,28 +2411,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>0.92623080999999996</c:v>
+                  <c:v>91.807158353366901</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.8874959</c:v>
+                  <c:v>48.6313141635489</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.86300752999999997</c:v>
+                  <c:v>40.819186563308897</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.84703196999999997</c:v>
+                  <c:v>35.136435439199303</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.82009149000000003</c:v>
+                  <c:v>22.921007561501</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.79847533000000004</c:v>
+                  <c:v>21.763458364151099</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.81461035000000004</c:v>
+                  <c:v>22.256909316418401</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.82532331999999997</c:v>
+                  <c:v>19.8327771950959</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2465,118 +2440,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4843-43BF-8508-4FA0F4F483BF}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$D$136</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>sum((3DAG(Level)-KDTree(Level))/# of Queries</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$B$137:$B$144</c:f>
-              <c:numCache>
-                <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>0.02</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.06</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.14000000000000001</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.22</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.26</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.3</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$D$137:$D$144</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>0.72309999999999997</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.7923</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.76249999999999996</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.71099999999999997</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.65329999999999999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.58240000000000003</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.5615</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.54290000000000005</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-4843-43BF-8508-4FA0F4F483BF}"/>
+              <c16:uniqueId val="{00000000-731C-48BB-9884-7FD284EF2161}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2588,11 +2452,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="725017008"/>
-        <c:axId val="725017968"/>
+        <c:axId val="1021063328"/>
+        <c:axId val="1021068608"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="725017008"/>
+        <c:axId val="1021063328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2649,12 +2513,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="725017968"/>
+        <c:crossAx val="1021068608"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="725017968"/>
+        <c:axId val="1021068608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2711,7 +2575,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="725017008"/>
+        <c:crossAx val="1021063328"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2723,8 +2587,65 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2738,7 +2659,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -2753,7 +2674,267 @@
           <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
-    </c:legend>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$136</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>sum((3DAG(Level)-KDTree(Level))/# of Queries</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$137:$B$144</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.14000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.22</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.26</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$D$137:$D$144</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.72309999999999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.7923</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.76249999999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.71099999999999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.65329999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.58240000000000003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.5615</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.54290000000000005</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1EEF-4287-B8B2-474B092FABAD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1021097888"/>
+        <c:axId val="1021100288"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1021097888"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1021100288"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1021100288"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1021097888"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -5862,6 +6043,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors16.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -9279,6 +9500,522 @@
 </file>
 
 <file path=xl/charts/style15.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style16.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -14431,22 +15168,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>611981</xdr:colOff>
+      <xdr:colOff>69055</xdr:colOff>
       <xdr:row>131</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:rowOff>42862</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>2381</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>107155</xdr:colOff>
       <xdr:row>146</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:rowOff>71437</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="16" name="Chart 15">
+        <xdr:cNvPr id="17" name="Chart 16">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C39CB1A-15BE-C1B4-1410-04312D68BE38}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFC936D6-1C19-CA00-EBCA-9DD32A2A385E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14459,6 +15196,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>511968</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>42862</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>550068</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>71437</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="18" name="Chart 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4584532-019F-BFB4-EA5E-1DCE870D3FE4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -15394,7 +16167,7 @@
         <v>0.02</v>
       </c>
       <c r="C137" s="2">
-        <v>0.92623080999999996</v>
+        <v>91.807158353366901</v>
       </c>
       <c r="D137" s="2">
         <v>0.72309999999999997</v>
@@ -15405,7 +16178,7 @@
         <v>0.06</v>
       </c>
       <c r="C138" s="2">
-        <v>0.8874959</v>
+        <v>48.6313141635489</v>
       </c>
       <c r="D138" s="2">
         <v>0.7923</v>
@@ -15416,7 +16189,7 @@
         <v>0.1</v>
       </c>
       <c r="C139" s="2">
-        <v>0.86300752999999997</v>
+        <v>40.819186563308897</v>
       </c>
       <c r="D139" s="2">
         <v>0.76249999999999996</v>
@@ -15427,7 +16200,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="C140" s="2">
-        <v>0.84703196999999997</v>
+        <v>35.136435439199303</v>
       </c>
       <c r="D140" s="2">
         <v>0.71099999999999997</v>
@@ -15438,7 +16211,7 @@
         <v>0.18</v>
       </c>
       <c r="C141" s="2">
-        <v>0.82009149000000003</v>
+        <v>22.921007561501</v>
       </c>
       <c r="D141" s="2">
         <v>0.65329999999999999</v>
@@ -15449,7 +16222,7 @@
         <v>0.22</v>
       </c>
       <c r="C142" s="2">
-        <v>0.79847533000000004</v>
+        <v>21.763458364151099</v>
       </c>
       <c r="D142" s="2">
         <v>0.58240000000000003</v>
@@ -15460,7 +16233,7 @@
         <v>0.26</v>
       </c>
       <c r="C143" s="2">
-        <v>0.81461035000000004</v>
+        <v>22.256909316418401</v>
       </c>
       <c r="D143" s="2">
         <v>0.5615</v>
@@ -15471,7 +16244,7 @@
         <v>0.3</v>
       </c>
       <c r="C144" s="2">
-        <v>0.82532331999999997</v>
+        <v>19.8327771950959</v>
       </c>
       <c r="D144" s="2">
         <v>0.54290000000000005</v>

--- a/3DAG and 2D Tree/Data Summaries/Gowalla 120143 points 1 - 10,000.xlsx
+++ b/3DAG and 2D Tree/Data Summaries/Gowalla 120143 points 1 - 10,000.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cvinc\Desktop\College\Internship\Github\Multi-Dimensional-Data-Structure\3DAG and 2D Tree\Data Summaries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E816849-62B4-4D20-A32D-1D5A99B9DE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F8D7E7-BAE0-4D39-AEBB-662BEF27CE96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{428F074D-1793-4279-8FD6-82BE55EE023D}"/>
+    <workbookView xWindow="11918" yWindow="0" windowWidth="12165" windowHeight="14362" xr2:uid="{428F074D-1793-4279-8FD6-82BE55EE023D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
